--- a/ExcelFiles/Monster.xlsx
+++ b/ExcelFiles/Monster.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OzProject\UnityProject\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8A5E80-6528-4656-A57E-041638D5AAF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8A372D-AC82-484E-B666-432CABD3F151}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6C81112B-CB61-4E6E-856E-F11AB94937B8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
   <si>
     <t>고유ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -190,6 +190,111 @@
   </si>
   <si>
     <t>Monster_07_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_02</t>
+  </si>
+  <si>
+    <t>BossMonster_03</t>
+  </si>
+  <si>
+    <t>BossMonster_04</t>
+  </si>
+  <si>
+    <t>BossMonster_05</t>
+  </si>
+  <si>
+    <t>BossMonster_06</t>
+  </si>
+  <si>
+    <t>CroSpider</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image/BossMonsters/BossMonster_01_idle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Image/BossMonsters/BossMonster_02_idle</t>
+  </si>
+  <si>
+    <t>Image/BossMonsters/BossMonster_03_idle</t>
+  </si>
+  <si>
+    <t>Image/BossMonsters/BossMonster_04_idle</t>
+  </si>
+  <si>
+    <t>Image/BossMonsters/BossMonster_05_idle</t>
+  </si>
+  <si>
+    <t>Image/BossMonsters/BossMonster_06_idle</t>
+  </si>
+  <si>
+    <t>BossMonster_01_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animator/BossMonster_01_controller</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_02_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_03_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_04_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_05_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BossMonster_06_idle_0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Animator/BossMonster_02_controller</t>
+  </si>
+  <si>
+    <t>Animator/BossMonster_03_controller</t>
+  </si>
+  <si>
+    <t>Animator/BossMonster_04_controller</t>
+  </si>
+  <si>
+    <t>Animator/BossMonster_05_controller</t>
+  </si>
+  <si>
+    <t>Animator/BossMonster_06_controller</t>
+  </si>
+  <si>
+    <t>Gorillra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GroundMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>JewelMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TimeMonster</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WaterDragon</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -554,11 +659,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F37E48F5-2C28-46F8-B85A-8058351F8C67}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="21.3984375" customWidth="1"/>
-    <col min="3" max="4" width="27.09765625" customWidth="1"/>
+    <col min="3" max="3" width="38.5" customWidth="1"/>
+    <col min="4" max="4" width="27.09765625" customWidth="1"/>
     <col min="5" max="5" width="30.296875" customWidth="1"/>
     <col min="6" max="6" width="23.19921875" customWidth="1"/>
     <col min="7" max="7" width="21.59765625" customWidth="1"/>
@@ -635,7 +741,7 @@
         <v>8</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
@@ -655,10 +761,10 @@
         <v>32</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G5">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
@@ -681,7 +787,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
@@ -701,10 +807,10 @@
         <v>34</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
@@ -724,10 +830,10 @@
         <v>35</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G8">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
@@ -747,10 +853,10 @@
         <v>36</v>
       </c>
       <c r="F9">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G9">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
@@ -773,7 +879,145 @@
         <v>8</v>
       </c>
       <c r="G10">
-        <v>3</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11">
+        <v>30</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" t="s">
+        <v>66</v>
+      </c>
+      <c r="F12">
+        <v>40</v>
+      </c>
+      <c r="G12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13">
+        <v>50</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>74</v>
+      </c>
+      <c r="C15" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15">
+        <v>70</v>
+      </c>
+      <c r="G15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
